--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -892,20 +892,14 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B23" s="3" t="n">
+        <v>0.292844</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>-0.025881</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>-0.118717</v>
       </c>
     </row>
     <row r="24">
@@ -1119,20 +1113,14 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1141,20 +1129,14 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1163,20 +1145,14 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1185,20 +1161,14 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1207,20 +1177,14 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1229,20 +1193,14 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1251,20 +1209,14 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0.027155</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0.003188</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0.008199</v>
       </c>
     </row>
     <row r="41">
@@ -1273,20 +1225,14 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.027155</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.003188</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0.008199</v>
       </c>
     </row>
     <row r="42">
@@ -1295,20 +1241,14 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1317,20 +1257,14 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1339,20 +1273,14 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1361,20 +1289,14 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1383,20 +1305,14 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1405,20 +1321,14 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1427,20 +1337,14 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1471,20 +1375,14 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1493,20 +1391,14 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1515,20 +1407,14 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1537,20 +1423,14 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1559,20 +1439,14 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1603,20 +1477,14 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1625,20 +1493,14 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1647,20 +1509,14 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1669,20 +1525,14 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1691,20 +1541,14 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1713,20 +1557,14 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -1773,20 +1611,14 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -1795,20 +1627,14 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -1817,20 +1643,14 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -1839,20 +1659,14 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.221075</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.117257</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.156057</v>
       </c>
     </row>
     <row r="68">
@@ -1861,20 +1675,14 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.221075</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.117257</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.156057</v>
       </c>
     </row>
     <row r="69">
@@ -1883,20 +1691,14 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0.012384</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.013888</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0.015388</v>
       </c>
     </row>
     <row r="70">
@@ -1905,20 +1707,14 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1927,20 +1723,14 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0.012384</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.013888</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0.015388</v>
       </c>
     </row>
     <row r="72">
@@ -1949,20 +1739,14 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -1971,20 +1755,14 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -1993,20 +1771,14 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2015,20 +1787,14 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2059,20 +1825,14 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2081,20 +1841,14 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2103,20 +1857,14 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2125,20 +1873,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>-0.03182091485130197</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>-0.03978924991190096</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>-0.03289749356502108</v>
       </c>
     </row>
     <row r="81">
@@ -2147,20 +1889,14 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2169,20 +1905,14 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2191,20 +1921,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2213,20 +1937,14 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2235,20 +1953,14 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2295,20 +2007,14 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>15.179115</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>15.245135</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>15.245135</v>
       </c>
     </row>
     <row r="89">
@@ -2317,20 +2023,14 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2355,20 +2055,14 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2377,20 +2071,14 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2399,20 +2087,14 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2421,20 +2103,14 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>-0.389178</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>-0.349039</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>-0.467756</v>
       </c>
     </row>
     <row r="95">
@@ -2443,20 +2119,14 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2465,20 +2135,14 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>-0.389178</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>-0.349039</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>-0.467756</v>
       </c>
     </row>
     <row r="97">
@@ -2487,20 +2151,14 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>-12.55372407341699</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>-19.30952644390352</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>-36.52061211742661</v>
       </c>
     </row>
     <row r="98">
@@ -2516,20 +2174,14 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>0.292844</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.025881</v>
+      </c>
+      <c r="D99" s="3" t="n">
+        <v>-0.118717</v>
       </c>
     </row>
     <row r="100">
@@ -2538,20 +2190,14 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2560,20 +2206,14 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2582,20 +2222,14 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2604,20 +2238,14 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D103" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -2626,20 +2254,14 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>-0.082786</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.044312</v>
+      </c>
+      <c r="D104" s="3" t="n">
+        <v>0.041283</v>
       </c>
     </row>
     <row r="105">
@@ -2648,20 +2270,14 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2670,20 +2286,14 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>-0.082786</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.044312</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.041283</v>
       </c>
     </row>
     <row r="107">
@@ -2692,20 +2302,14 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2714,20 +2318,14 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2736,20 +2334,14 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2758,20 +2350,14 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2780,20 +2366,14 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2802,20 +2382,14 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2824,20 +2398,14 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2846,20 +2414,14 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2868,20 +2430,14 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2890,20 +2446,14 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2912,20 +2462,14 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2934,20 +2478,14 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2959,15 +2497,11 @@
       <c r="B119" s="3" t="n">
         <v>-0.041299</v>
       </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="C119" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D119" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -2976,20 +2510,14 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2998,20 +2526,14 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -3020,20 +2542,14 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -3042,20 +2558,14 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -3064,20 +2574,14 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -3086,20 +2590,14 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -3108,20 +2606,14 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3152,20 +2644,14 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3206,20 +2692,14 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3228,20 +2708,14 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.002649</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>0.011052</v>
+      </c>
+      <c r="D132" s="3" t="n">
+        <v>-0.010279</v>
       </c>
     </row>
     <row r="133">
@@ -3266,20 +2740,14 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3288,20 +2756,14 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.084136</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.073509</v>
+      </c>
+      <c r="D135" s="3" t="n">
+        <v>-0.047279</v>
       </c>
     </row>
   </sheetData>
@@ -3315,7 +2777,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3433,7 +2895,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E4" s="5" t="n">
         <v>0.027155</v>
       </c>
@@ -3524,7 +2990,11 @@
           <t>Trade payables and accrued liabilities 13</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CurrentAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E7" s="5" t="n">
         <v>0.221075</v>
       </c>
@@ -3551,7 +3021,11 @@
           <t>Loan Payable 15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E8" s="5" t="n">
         <v>0.012384</v>
       </c>
@@ -3732,7 +3206,11 @@
           <t>Total shareholders’ (deficit) equity</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>-0.389178</v>
       </c>
@@ -4470,7 +3948,11 @@
           <t>Gain (Loss) for the period</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
         <v>0.292844</v>
       </c>
@@ -4613,7 +4095,11 @@
           <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -4733,7 +4219,11 @@
           <t>Change in cash during the period</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>-0.002649</v>
       </c>
@@ -5064,7 +4554,11 @@
           <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E61" s="5" t="n">
         <v>-0.082786</v>
       </c>
@@ -5268,2292 +4762,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>St. Catharines, Ontario</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>April</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>0.002025</v>
-      </c>
-      <c r="F68" s="5" t="n">
-        <v>0.002026</v>
-      </c>
-      <c r="G68" s="5" t="n">
-        <v>2.9e-05</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>St. Catharines, Ontario</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>As at December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F69" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G69" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.000125</v>
-      </c>
-      <c r="F70" s="5" t="n">
-        <v>0.011177</v>
-      </c>
-      <c r="G70" s="5" t="n">
-        <v>0.000898</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>HST receivable</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
-      <c r="E71" s="5" t="n">
-        <v>0.027155</v>
-      </c>
-      <c r="F71" s="5" t="n">
-        <v>0.003188</v>
-      </c>
-      <c r="G71" s="5" t="n">
-        <v>0.008199</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Prepaid expenses and other assets 7</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>0.003711</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>0.003711</v>
-      </c>
-      <c r="G72" s="5" t="n">
-        <v>0.003711</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F73" s="5" t="n">
-        <v>0.018076</v>
-      </c>
-      <c r="G73" s="5" t="n">
-        <v>0.012808</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Trade payables and accrued liabilities 13</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>0.221075</v>
-      </c>
-      <c r="F74" s="5" t="n">
-        <v>0.117257</v>
-      </c>
-      <c r="G74" s="5" t="n">
-        <v>0.156057</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Loan Payable 15</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
-      <c r="E75" s="5" t="n">
-        <v>0.012384</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>0.013888</v>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.015388</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Due to directors and related parties 13</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0.18672</v>
-      </c>
-      <c r="F76" s="5" t="n">
-        <v>0.23597</v>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>0.309119</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Total liabilities</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
-      <c r="E77" s="5" t="n">
-        <v>0.420179</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>0.367115</v>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.480564</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr"/>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Share capital 10</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>15.179115</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>15.245135</v>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>15.245135</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Warrant reserve 10</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" s="5" t="n">
-        <v>1.181887</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>1.181887</v>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>1.181887</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr"/>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Share based payment reserve 11</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
-      <c r="E80" s="5" t="n">
-        <v>0.684818</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>0.684818</v>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.684818</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr"/>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Deficit</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
-      <c r="E81" s="5" t="n">
-        <v>-17.434998</v>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>-17.460879</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>-17.579596</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Total shareholders’ (deficit) equity</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" s="5" t="n">
-        <v>-0.389178</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>-0.349039</v>
-      </c>
-      <c r="G82" s="5" t="n">
-        <v>-0.467756</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Total liabilities and shareholders’ equity</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.031001</v>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>0.018076</v>
-      </c>
-      <c r="G83" s="5" t="n">
-        <v>0.012808</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Director Director</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>As at December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G84" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Consulting and management fees</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
-      <c r="E85" s="5" t="n">
-        <v>0.01299</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>0.001099</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>General and administrative</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E86" s="5" t="n">
-        <v>0.027048</v>
-      </c>
-      <c r="F86" s="5" t="n">
-        <v>0.016102</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>0.012333</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Professional fees</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="n">
-        <v>0.053887</v>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>0.125347</v>
-      </c>
-      <c r="G87" s="5" t="n">
-        <v>0.071218</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Operating expenses</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Operating expenses total</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" s="5" t="n">
-        <v>0.09392499999999999</v>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>0.142548</v>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>0.083551</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Interest (expense) income</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.027508</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.035166</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Gain on debt settlement 10</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" s="5" t="n">
-        <v>0.452869</v>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>0.144185</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Impairment of investments 8</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" s="5" t="n">
-        <v>-0.014685</v>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>-1e-05</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Other items total</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" s="5" t="n">
-        <v>0.413383</v>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.116667</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.035166</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Net gain (loss) and comprehensive loss</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" s="5" t="n">
-        <v>0.292844</v>
-      </c>
-      <c r="F93" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-0.118717</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Earning per share –</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Basic 12</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-      <c r="E94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Earning per share –</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Diluted 12</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-      <c r="E95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>shares outstanding</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Basic 12</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-      <c r="E96" s="5" t="n">
-        <v>77.987296</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>83.452319</v>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>84.441889</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>shares outstanding</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Diluted 12</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" s="5" t="n">
-        <v>77.987296</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>83.452319</v>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>84.441889</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>shares outstanding</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>As at December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Reserve</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2023 80,237,785 15,179,115 1,181,887 684,818</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>-0.389178</v>
-      </c>
-      <c r="G99" s="5" t="n">
-        <v>-17.434998</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Shares issued on debt</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>10 4,204,104 66,020 - -</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.06602</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Net comprehensive loss for</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>- - - -</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-      <c r="E101" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-      <c r="G101" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>current year</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2024 84,441,889 15,245,135 1,181,887 684,818</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-      <c r="E102" s="5" t="n">
-        <v>-0.349039</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>-0.349039</v>
-      </c>
-      <c r="G102" s="5" t="n">
-        <v>-17.460879</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>current year</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2025 84,441,889 15,245,135 1,181,887 684,818</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>-0.467756</v>
-      </c>
-      <c r="G103" s="5" t="n">
-        <v>-17.579596</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>current year</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>As at December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>0.002024</v>
-      </c>
-      <c r="G104" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Operating activities</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Gain (Loss) for the period</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" s="5" t="n">
-        <v>0.292844</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-      <c r="G105" s="5" t="n">
-        <v>-0.118717</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Impairment of investments 8</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Gain ondebtsettlement</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>-0.144185</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Interest (income) expense</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-      <c r="E108" s="5" t="n">
-        <v>0.024801</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>0.027508</v>
-      </c>
-      <c r="G108" s="5" t="n">
-        <v>0.035166</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>HST receivable</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" s="5" t="n">
-        <v>0.002627</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.024727</v>
-      </c>
-      <c r="G109" s="5" t="n">
-        <v>-0.005011</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>0.044312</v>
-      </c>
-      <c r="G110" s="5" t="n">
-        <v>0.041283</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Changes in non-cash working capital</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>-0.073509</v>
-      </c>
-      <c r="G111" s="5" t="n">
-        <v>-0.047279</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Advances (net of repayment) received from directors and</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Advances (net of repayment) received from directors and total</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-      <c r="E112" s="5" t="n">
-        <v>0.122786</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>0.084561</v>
-      </c>
-      <c r="G112" s="5" t="n">
-        <v>0.037</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>related parties</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Cash provided by financing activities</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" s="5" t="n">
-        <v>0.122786</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0.084561</v>
-      </c>
-      <c r="G113" s="5" t="n">
-        <v>0.037</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>related parties</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Change in cash during the period</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" s="5" t="n">
-        <v>-0.002649</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0.011052</v>
-      </c>
-      <c r="G114" s="5" t="n">
-        <v>-0.010279</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>related parties</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Cash, beginning of period</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr"/>
-      <c r="E115" s="5" t="n">
-        <v>0.002774</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0.000125</v>
-      </c>
-      <c r="G115" s="5" t="n">
-        <v>0.011177</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>related parties</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-      <c r="E116" s="5" t="n">
-        <v>0.000125</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.011177</v>
-      </c>
-      <c r="G116" s="5" t="n">
-        <v>0.000898</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>St. Catharines, Ontario</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>As at December 31, 2024 and December</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-      <c r="E117" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Current</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Current total</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" s="5" t="n">
-        <v>0.030991</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.018076</v>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Long Term</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Other investments</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-      <c r="E119" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Long Term</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Long Term total</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-      <c r="E120" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Long Term</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Total Assets</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-      <c r="E121" s="5" t="n">
-        <v>0.031001</v>
-      </c>
-      <c r="F121" s="5" t="n">
-        <v>0.018076</v>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Director Director</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>As at December 31, 2024 and December</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-      <c r="E122" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Interest (expense) income (</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" s="5" t="n">
-        <v>-0.024801</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.027508</v>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Loss on foreign exchange</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Share of Associate 8</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-      <c r="E125" s="5" t="n">
-        <v>-0.026614</v>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>shares outstanding</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>As at December 31, 2024 and December</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-      <c r="E126" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F126" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Reserve</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Balance, December</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-      <c r="E127" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F127" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Reserve</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>62,760,586 14,916,957 1,181,887 684,818</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" s="5" t="n">
-        <v>-0.944181</v>
-      </c>
-      <c r="F128" s="5" t="n">
-        <v>-17.727842</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Shares issued on debt</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>10 17,477,199 262,158 - -</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-      <c r="E129" s="5" t="n">
-        <v>0.262158</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Net comprehensive gain for</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>- - - -</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-      <c r="E130" s="5" t="n">
-        <v>0.292844</v>
-      </c>
-      <c r="F130" s="5" t="n">
-        <v>0.292844</v>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>the period</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Balance, December 31, 2023 80,237,785 15,179,115 1,181,887 6 84,818</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-      <c r="E131" s="5" t="n">
-        <v>-0.389178</v>
-      </c>
-      <c r="F131" s="5" t="n">
-        <v>-17.434998</v>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Shares issued on debt</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>10 66,020 - -</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-      <c r="E132" s="5" t="n">
-        <v>0.06602</v>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>current year</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>As at December 31, 2024 and December</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
-      <c r="E133" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F133" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Impairment ofinvestments 8</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr"/>
-      <c r="E134" s="5" t="n">
-        <v>0.014685</v>
-      </c>
-      <c r="F134" s="5" t="n">
-        <v>1e-05</v>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Impairment of intangibles and goodwill</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Share of Associate 8</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr"/>
-      <c r="E136" s="5" t="n">
-        <v>0.026614</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Bad debt</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr"/>
-      <c r="E137" s="5" t="n">
-        <v>0.00642</v>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Gain on share settlement</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
-      <c r="E138" s="5" t="n">
-        <v>-0.452869</v>
-      </c>
-      <c r="F138" s="5" t="n">
-        <v>-0.144185</v>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>activities</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>FX loss</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Prepaid expenses and other assets 7</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr"/>
-      <c r="E140" s="5" t="n">
-        <v>0.08352800000000001</v>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr"/>
-      <c r="E141" s="5" t="n">
-        <v>-0.082786</v>
-      </c>
-      <c r="F141" s="5" t="n">
-        <v>0.044312</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Cash used inoperating activities</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr"/>
-      <c r="E142" s="5" t="n">
-        <v>-0.084136</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>-0.073509</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Investing activities</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Investment in GG Hub</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr"/>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>8e-06</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>(43,867)</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Proceed of Sale 8</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>0.002568</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>(43,867)</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Cash used ininvestingactivities</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr"/>
-      <c r="E145" s="5" t="n">
-        <v>-0.041299</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Receipts on options exercised 11</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr"/>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Paymentof debt to MotionPix</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr"/>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -431,6 +431,12 @@
   </sheetPr>
   <dimension ref="A1:D135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -2783,7 +2783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3262,7 +3262,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director       Director</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -3410,10 +3410,8 @@
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>-0.024801</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>-0.027508</v>
@@ -3799,7 +3797,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Director Director</t>
+          <t>Director       Director</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -3833,15 +3831,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Interest (expense) income (</t>
+          <t>Loss on foreign exchange</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" s="5" t="n">
-        <v>-0.024801</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>0.027508</v>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3862,14 +3864,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Loss on foreign exchange</t>
+          <t>Share of Associate 8</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E38" s="5" t="n">
+        <v>-0.026614</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3885,32 +3885,26 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>balance_sheet</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Other items</t>
-        </is>
-      </c>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share of Associate 8</t>
+          <t>As at December 31, 2025 and December</t>
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" s="5" t="n">
-        <v>-0.026614</v>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.002024</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
     </row>
     <row r="40">
@@ -3919,23 +3913,29 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Operating activities</t>
+        </is>
+      </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>As at December 31, 2025 and December</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Gain (Loss) for the period</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.292844</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>0.002024</v>
+        <v>-0.025881</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.118717</v>
       </c>
     </row>
     <row r="41">
@@ -3946,27 +3946,25 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Operating activities</t>
+          <t>activities</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Gain (Loss) for the period</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
+          <t>Impairment of investments 8</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" s="5" t="n">
-        <v>0.292844</v>
+        <v>0.014685</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-0.025881</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>-0.118717</v>
+        <v>1e-05</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
@@ -3982,7 +3980,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Impairment of investments 8</t>
+          <t>Gain on debt settlement</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -3992,7 +3990,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>1e-05</v>
+        <v>-0.144185</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4013,22 +4011,18 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Gain ondebtsettlement</t>
+          <t>Interest (income) expense</t>
         </is>
       </c>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E43" s="5" t="n">
+        <v>0.024801</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-0.144185</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.027508</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.035166</v>
       </c>
     </row>
     <row r="44">
@@ -4039,23 +4033,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>Changes in non-cash working capital</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Interest (income) expense</t>
+          <t>HST receivable</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
       <c r="E44" s="5" t="n">
-        <v>0.024801</v>
+        <v>0.002627</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.027508</v>
+        <v>0.024727</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.035166</v>
+        <v>-0.005011</v>
       </c>
     </row>
     <row r="45">
@@ -4071,18 +4065,24 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HST receivable</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" s="5" t="n">
-        <v>0.002627</v>
+          <t>Trade payables and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.024727</v>
+        <v>0.044312</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.005011</v>
+        <v>0.041283</v>
       </c>
     </row>
     <row r="46">
@@ -4098,12 +4098,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4112,10 +4112,10 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.044312</v>
+        <v>-0.073509</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.041283</v>
+        <v>-0.047279</v>
       </c>
     </row>
     <row r="47">
@@ -4126,29 +4126,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital</t>
+          <t>Advances (net of repayment) received from directors and</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cash used in operating activities</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Advances (net of repayment) received from directors and total</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>0.122786</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>-0.073509</v>
+        <v>0.084561</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.047279</v>
+        <v>0.037</v>
       </c>
     </row>
     <row r="48">
@@ -4159,15 +4153,19 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Advances (net of repayment) received from directors and</t>
+          <t>related parties</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Advances (net of repayment) received from directors and total</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr"/>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>0.122786</v>
       </c>
@@ -4191,22 +4189,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cash provided by financing activities</t>
+          <t>Change in cash during the period</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>ChangesInCash</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>0.122786</v>
+        <v>-0.002649</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.084561</v>
+        <v>0.011052</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.037</v>
+        <v>-0.010279</v>
       </c>
     </row>
     <row r="50">
@@ -4222,22 +4220,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Change in cash during the period</t>
+          <t>Cash, beginning of period</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>BeginningCashPosition</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>-0.002649</v>
+        <v>0.002774</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.011052</v>
+        <v>0.000125</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.010279</v>
+        <v>0.011177</v>
       </c>
     </row>
     <row r="51">
@@ -4253,22 +4251,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cash, beginning of period</t>
+          <t>Cash, end of period</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>EndCashPosition</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.002774</v>
+        <v>0.000125</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>0.000125</v>
+        <v>0.011177</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.011177</v>
+        <v>0.000898</v>
       </c>
     </row>
     <row r="52">
@@ -4277,29 +4275,23 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>related parties</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cash, end of period</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>As at December 31, 2024 and December</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
       <c r="E52" s="5" t="n">
-        <v>0.000125</v>
+        <v>0.002023</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>0.011177</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>0.000898</v>
+        <v>3.1e-05</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="53">
@@ -4308,18 +4300,26 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>activities</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>As at December 31, 2024 and December</t>
+          <t>Impairment of intangibles and goodwill</t>
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>3.1e-05</v>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -4340,15 +4340,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Impairment ofinvestments 8</t>
+          <t>Share of Associate 8</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>0.014685</v>
-      </c>
-      <c r="F54" s="5" t="n">
-        <v>1e-05</v>
+        <v>0.026614</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -4369,14 +4371,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Impairment of intangibles and goodwill</t>
+          <t>Bad debt</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="5" t="n">
+        <v>0.00642</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -4402,17 +4402,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Share of Associate 8</t>
+          <t>Gain on share settlement</t>
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
       <c r="E56" s="5" t="n">
-        <v>0.026614</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.452869</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.144185</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -4433,12 +4431,14 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bad debt</t>
+          <t>FX loss</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>0.00642</v>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -4459,20 +4459,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Gain on share settlement</t>
+          <t>Prepaid expenses and other assets 7</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
       <c r="E58" s="5" t="n">
-        <v>-0.452869</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>-0.144185</v>
+        <v>0.08352800000000001</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -4488,24 +4490,24 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>activities</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>FX loss</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Trade payables and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>-0.082786</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>0.044312</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -4526,17 +4528,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Prepaid expenses and other assets 7</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Cash used in operating activities</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
-        <v>0.08352800000000001</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.084136</v>
+      </c>
+      <c r="F60" s="5" t="n">
+        <v>-0.073509</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -4552,24 +4556,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>Investing activities</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="n">
-        <v>-0.082786</v>
+          <t>Investment in GG Hub</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" s="5" t="n">
-        <v>0.044312</v>
+        <v>8e-06</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -4585,24 +4587,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
+          <t>(43,867)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Cash used inoperating activities</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>Proceed of Sale 8</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>-0.084136</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.073509</v>
+        <v>0.002568</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -4618,22 +4618,26 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Investing activities</t>
+          <t>(43,867)</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Investment in GG Hub</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>8e-06</v>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="n">
+        <v>-0.041299</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -4649,17 +4653,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>(43,867)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Proceed of Sale 8</t>
+          <t>Receipts on options exercised 11</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" s="5" t="n">
-        <v>0.002568</v>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -4680,21 +4686,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>(43,867)</t>
+          <t>Financing activities</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cash used ininvestingactivities</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="n">
-        <v>-0.041299</v>
+          <t>Payment of debt to MotionPix</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -4702,72 +4706,6 @@
         </is>
       </c>
       <c r="G65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Receipts on options exercised 11</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>cash_flow</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Financing activities</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Paymentof debt to MotionPix</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -2078,13 +2078,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.866705</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.866705</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.866705</v>
       </c>
     </row>
     <row r="93">
@@ -3139,7 +3139,11 @@
           <t>Warrant reserve 10</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>1.181887</v>
       </c>
@@ -3162,7 +3166,11 @@
           <t>Share based payment reserve 11</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" s="5" t="n">
         <v>0.684818</v>
       </c>

--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.011177</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000898</v>
       </c>
     </row>
     <row r="35">
@@ -1152,13 +1152,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.000125</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.011177</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000898</v>
       </c>
     </row>
     <row r="37">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">

--- a/output/pdf_financials_xlsx/PLAY.xlsx
+++ b/output/pdf_financials_xlsx/PLAY.xlsx
@@ -2213,13 +2213,13 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>0.002627</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
+        <v>0.024727</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005011</v>
       </c>
     </row>
     <row r="102">
@@ -2293,13 +2293,13 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>-0.082786</v>
+        <v>-0.08015899999999999</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.044312</v>
+        <v>0.069039</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.041283</v>
+        <v>0.036272</v>
       </c>
     </row>
     <row r="107">
@@ -4049,7 +4049,11 @@
           <t>HST receivable</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr"/>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E44" s="5" t="n">
         <v>0.002627</v>
       </c>
